--- a/sekigae/data/sample.xlsx
+++ b/sekigae/data/sample.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/var/mobile/Containers/Data/Application/3D42F47C-9621-491E-903C-A0C9E12E4E0B/Library/Application Support/Drafts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:41000001_{F6C23036-635D-C642-99B7-A579C98A3792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C400038D-EE01-D04B-A1AF-9F7D6C82673C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>東貫太 衛藤凛 小幡桜介 笠木陽希 木崎公亮 佐藤大悟 佐藤葉緒 竹尾航士郎 玉井こよみ 利光咲生菜 又野真穂 光増耕太郎 三戸颯馬 宮田果歩</t>
   </si>
@@ -74,9 +74,6 @@
     <t>xoooox oooooo oooooo oooooo xoooox</t>
   </si>
   <si>
-    <t>xoooox oooooo oooooo oooooo oooooo oooooo ooooo</t>
-  </si>
-  <si>
     <t xml:space="preserve">麻生侑愛 上野瑛人 上野峻 甲斐飛登 角田佐衣 北山昊樹 小出理央 椎原悠貴 重石優心 篠崎未來 首藤晴 造士桜 田北海翔 立和田悠人 中田拓臣 中野翔太 西村周悟 野仲勇希 濱永真仁 姫野愛菜 廣田瑠亜 堀田一彰 前村尚 松尾優汰 三浦琉生 吉田莉里那 </t>
   </si>
   <si>
@@ -93,6 +90,9 @@
   </si>
   <si>
     <t>25 7 6</t>
+  </si>
+  <si>
+    <t>xoooox oooooo oooooo oooooo oooooo oooooo oooooo</t>
   </si>
 </sst>
 </file>
@@ -497,10 +497,10 @@
         <v>7</v>
       </c>
       <c r="H1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1" t="s">
         <v>16</v>
-      </c>
-      <c r="I1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
@@ -549,13 +549,13 @@
         <v>12</v>
       </c>
       <c r="G3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H3">
         <v>1</v>
       </c>
       <c r="I3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
@@ -575,16 +575,16 @@
         <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H4">
         <v>1</v>
       </c>
       <c r="I4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
